--- a/자소서/홍석진 취업/채용트래커/채용공고_홍석진_20260615.xlsx
+++ b/자소서/홍석진 취업/채용트래커/채용공고_홍석진_20260615.xlsx
@@ -18,13 +18,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00999999"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,14 +483,6 @@
           <t>▌🏢 대기업</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -513,7 +518,7 @@
           <t>자동차부품, OE영업, 글로벌</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -558,7 +563,7 @@
           <t>화학, 해외영업, 석유화학</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -603,12 +608,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -639,8 +643,7 @@
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -685,12 +688,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -721,13 +723,11 @@
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -763,12 +763,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -804,12 +803,11 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -835,18 +833,16 @@
           <t>1년+</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -867,19 +863,16 @@
           <t>B2B/B2C 온라인MD 3년이상</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -900,15 +893,11 @@
           <t>온/오프라인 채널 관리자(MD, 영업)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,15 +918,11 @@
           <t>오프라인 기반 영업 담당자</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -958,15 +943,11 @@
           <t>[로보락] 오프라인 영업 4~7년</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1002,12 +983,11 @@
           <t>대기업, BD, 무역, 신입</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,12 +1023,11 @@
           <t>현대가, B2B, 제휴영업</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1084,12 +1063,11 @@
           <t>화학, 해외영업, 석유화학</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1097,14 +1075,6 @@
           <t>▌🌍 외국계</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1140,12 +1110,11 @@
           <t>BD, 바이오</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1181,12 +1150,11 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1222,12 +1190,11 @@
           <t>화학, B2B</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1263,12 +1230,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1304,12 +1270,11 @@
           <t>SCM</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1340,13 +1305,11 @@
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1382,12 +1345,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1423,12 +1385,11 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1464,12 +1425,11 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1500,13 +1460,11 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1537,13 +1495,11 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1579,12 +1535,11 @@
           <t>외국계, 종합상사, 순환경제</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1592,14 +1547,6 @@
           <t>▌🏭 중견기업</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1635,12 +1582,11 @@
           <t>화학, 해외영업, 중견</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1676,12 +1622,11 @@
           <t>화장품원료, 해외영업, B2B</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1717,12 +1662,11 @@
           <t>자동차부품, 해외영업, 제조</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1758,12 +1702,11 @@
           <t>소비재, 해외영업, 수출입</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1799,12 +1742,11 @@
           <t>철강, 해외영업, 소재</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1840,14 +1782,28 @@
           <t>화장품, B2B, 글로벌, 대기업</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1914,14 +1870,6 @@
           <t>▌🏢 대기업</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1957,7 +1905,7 @@
           <t>자동차부품, OE영업, 글로벌</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2002,7 +1950,7 @@
           <t>화학, 해외영업, 석유화학</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2047,12 +1995,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2083,8 +2030,7 @@
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2129,12 +2075,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2165,13 +2110,11 @@
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2207,12 +2150,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2248,12 +2190,11 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2279,18 +2220,16 @@
           <t>1년+</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2311,19 +2250,16 @@
           <t>B2B/B2C 온라인MD 3년이상</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2344,15 +2280,11 @@
           <t>온/오프라인 채널 관리자(MD, 영업)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2373,15 +2305,11 @@
           <t>오프라인 기반 영업 담당자</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2402,15 +2330,11 @@
           <t>[로보락] 오프라인 영업 4~7년</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2446,12 +2370,11 @@
           <t>대기업, BD, 무역, 신입</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2487,12 +2410,11 @@
           <t>현대가, B2B, 제휴영업</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2528,12 +2450,11 @@
           <t>화학, 해외영업, 석유화학</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2541,14 +2462,6 @@
           <t>▌🌍 외국계</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2584,12 +2497,11 @@
           <t>BD, 바이오</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2625,12 +2537,11 @@
           <t>화학, B2B</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2666,12 +2577,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2707,12 +2617,11 @@
           <t>SCM</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2743,13 +2652,11 @@
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2785,12 +2692,11 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2826,12 +2732,11 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2867,12 +2772,11 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2903,13 +2807,11 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2945,12 +2847,11 @@
           <t>외국계, 종합상사, 순환경제</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2958,14 +2859,6 @@
           <t>▌🏭 중견기업</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3001,12 +2894,11 @@
           <t>화학, 해외영업, 중견</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3042,12 +2934,11 @@
           <t>화장품원료, 해외영업, B2B</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3083,12 +2974,11 @@
           <t>자동차부품, 해외영업, 제조</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3124,12 +3014,11 @@
           <t>소비재, 해외영업, 수출입</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3165,12 +3054,11 @@
           <t>철강, 해외영업, 소재</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3206,14 +3094,28 @@
           <t>화장품, B2B, 글로벌, 대기업</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>🔗 지원하기</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/자소서/홍석진 취업/채용트래커/채용공고_홍석진_20260615.xlsx
+++ b/자소서/홍석진 취업/채용트래커/채용공고_홍석진_20260615.xlsx
@@ -688,7 +688,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -723,7 +723,7 @@
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -763,7 +763,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -803,7 +803,7 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -838,7 +838,7 @@
           <t>B2B</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -868,7 +868,7 @@
           <t>B2B</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -893,7 +893,7 @@
           <t>온/오프라인 채널 관리자(MD, 영업)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -918,7 +918,7 @@
           <t>오프라인 기반 영업 담당자</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -943,7 +943,7 @@
           <t>[로보락] 오프라인 영업 4~7년</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1110,7 +1110,7 @@
           <t>BD, 바이오</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1150,7 +1150,7 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1190,7 +1190,7 @@
           <t>화학, B2B</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1230,7 +1230,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1270,7 +1270,7 @@
           <t>SCM</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1305,7 +1305,7 @@
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1345,7 +1345,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1385,7 +1385,7 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1425,7 +1425,7 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1460,7 +1460,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1495,7 +1495,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1535,7 +1535,7 @@
           <t>외국계, 종합상사, 순환경제</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -1794,15 +1794,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2075,7 +2096,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2110,7 +2131,7 @@
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2150,7 +2171,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2190,7 +2211,7 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2225,7 +2246,7 @@
           <t>B2B</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2255,7 +2276,7 @@
           <t>B2B</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2280,7 +2301,7 @@
           <t>온/오프라인 채널 관리자(MD, 영업)</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2305,7 +2326,7 @@
           <t>오프라인 기반 영업 담당자</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2330,7 +2351,7 @@
           <t>[로보락] 오프라인 영업 4~7년</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2497,7 +2518,7 @@
           <t>BD, 바이오</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2537,7 +2558,7 @@
           <t>화학, B2B</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2577,7 +2598,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2617,7 +2638,7 @@
           <t>SCM</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2652,7 +2673,7 @@
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2692,7 +2713,7 @@
           <t>BD</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2732,7 +2753,7 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2772,7 +2793,7 @@
           <t>해외영업</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2807,7 +2828,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -2847,7 +2868,7 @@
           <t>외국계, 종합상사, 순환경제</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="1" t="inlineStr">
         <is>
           <t>🔗 지원하기</t>
         </is>
@@ -3106,15 +3127,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
